--- a/data/evaluation_results_6.xlsx
+++ b/data/evaluation_results_6.xlsx
@@ -13,9 +13,9 @@
     <sheet name="Metadata" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Runs'!$A$1:$K$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Runs'!$A$1:$J$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Prompts'!$A$1:$B$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Scores'!$A$1:$B$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Scores'!$A$1:$B$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Metadata'!$A$1:$B$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -439,11 +439,10 @@
     <col width="50" customWidth="1" min="4" max="4"/>
     <col width="50" customWidth="1" min="5" max="5"/>
     <col width="34" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
-    <col width="23" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -479,25 +478,20 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>ttft_seconds</t>
+          <t>total_latency_seconds</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>total_latency_seconds</t>
+          <t>input_tokens</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>input_tokens</t>
+          <t>output_tokens</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>output_tokens</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>error</t>
         </is>
@@ -527,22 +521,19 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21T18:02:06.855087+00:00</t>
+          <t>2026-10-22T04:33:31.934328+00:00</t>
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.460503443999869</v>
+        <v>0.4339022619997195</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.4784080269998867</v>
+        <v>72</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>72</v>
-      </c>
-      <c r="J2" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="K2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -563,27 +554,24 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>The most likely consequence for the student is detention, loss of privileges, or a warning from the teacher or school administration.</t>
+          <t>The most likely consequence for the student would be detention, loss of privileges, or a warning from the teacher or school administration.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21T18:02:07.333803+00:00</t>
+          <t>2026-10-22T04:33:32.368528+00:00</t>
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.3623632159999488</v>
+        <v>0.3555643419999797</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.3750983459999588</v>
+        <v>72</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>72</v>
-      </c>
-      <c r="J3" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="K3" s="2" t="inlineStr"/>
+        <v>26</v>
+      </c>
+      <c r="J3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -604,27 +592,24 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>The most likely consequence for the student would be detention, suspension, or a warning, depending on the school's policies and the severity of the infraction.</t>
+          <t>The most likely consequence for the student would be detention, loss of privileges, or a warning from the teacher or school administration.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21T18:02:07.709115+00:00</t>
+          <t>2026-10-22T04:33:32.724310+00:00</t>
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.4063642880000771</v>
+        <v>0.3413818919998448</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.4183438679999654</v>
+        <v>72</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>72</v>
-      </c>
-      <c r="J4" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="K4" s="2" t="inlineStr"/>
+        <v>26</v>
+      </c>
+      <c r="J4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -645,7 +630,55 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Let's denote the cost of the ball as x.
+          <t>Let's say the ball costs x dollars.
+Since the bat costs $1.00 more than the ball, the bat costs x + $1.00.
+The total cost of the bat and the ball together is $1.10, so we can set up the equation:
+x + (x + $1.00) = $1.10
+Combine like terms:
+2x + $1.00 = $1.10
+Subtract $1.00 from both sides:
+2x = $0.10
+Divide both sides by 2:
+x = $0.05
+The ball costs $0.05.</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22T04:33:33.065912+00:00</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>1.375759520999964</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>69</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>131</v>
+      </c>
+      <c r="J5" s="2" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>A bat and a ball together cost $1.10. The bat costs $1.00 more than the ball. How much does the ball cost?</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Let's say the ball costs x dollars. 
 Since the bat costs $1.00 more than the ball, the bat costs x + $1.00.
 The total cost of the bat and the ball together is $1.10, so we can set up the equation:
 x + (x + $1.00) = $1.10
@@ -657,46 +690,43 @@
 x = $0.05</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-21T18:02:08.127666+00:00</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>1.18470590700008</v>
-      </c>
-      <c r="H5" s="2" t="n">
-        <v>1.200694190999911</v>
-      </c>
-      <c r="I5" s="2" t="n">
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22T04:33:34.441959+00:00</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>1.244194088999848</v>
+      </c>
+      <c r="H6" s="2" t="n">
         <v>69</v>
       </c>
-      <c r="J5" s="2" t="n">
-        <v>124</v>
-      </c>
-      <c r="K5" s="2" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="I6" s="2" t="n">
+        <v>123</v>
+      </c>
+      <c r="J6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="B7" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>A bat and a ball together cost $1.10. The bat costs $1.00 more than the ball. How much does the ball cost?</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Let's say the ball costs x dollars. 
-The bat costs $1.00 more than the ball, so the bat costs x + $1.00.
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Let's say the ball costs x dollars.
+Since the bat costs $1.00 more than the ball, the bat costs x + $1.00.
 The total cost of the bat and the ball together is $1.10, so we can set up the equation:
 x + (x + $1.00) = $1.10
 Combine like terms:
@@ -708,72 +738,21 @@
 The ball costs $0.05.</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-21T18:02:09.328583+00:00</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>1.276177433999919</v>
-      </c>
-      <c r="H6" s="2" t="n">
-        <v>1.297308388999909</v>
-      </c>
-      <c r="I6" s="2" t="n">
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22T04:33:35.686382+00:00</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>1.524199468000006</v>
+      </c>
+      <c r="H7" s="2" t="n">
         <v>69</v>
       </c>
-      <c r="J6" s="2" t="n">
-        <v>132</v>
-      </c>
-      <c r="K6" s="2" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>A bat and a ball together cost $1.10. The bat costs $1.00 more than the ball. How much does the ball cost?</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Let's say the ball costs x dollars. 
-Since the bat costs $1.00 more than the ball, the bat costs x + $1.00.
-The total cost of the bat and the ball together is $1.10. 
-So, we can set up the equation: x + (x + $1.00) = $1.10
-Combine like terms: 2x + $1.00 = $1.10
-Subtract $1.00 from both sides: 2x = $0.10
-Divide both sides by 2: x = $0.05
-The ball costs $0.05.</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-21T18:02:10.626114+00:00</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="n">
-        <v>1.304244148999942</v>
-      </c>
-      <c r="H7" s="2" t="n">
-        <v>1.322406367999974</v>
-      </c>
       <c r="I7" s="2" t="n">
-        <v>69</v>
-      </c>
-      <c r="J7" s="2" t="n">
-        <v>136</v>
-      </c>
-      <c r="K7" s="2" t="inlineStr"/>
+        <v>131</v>
+      </c>
+      <c r="J7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -794,29 +773,28 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>To solve this, we need to calculate the net progress the snail makes each day. 
-The snail climbs 3 feet up and slips back 2 feet, so it makes a net progress of 3 - 2 = 1 foot per day.
-Since the well is 20 feet deep, the snail will need 20 days to climb 20 feet.</t>
+          <t>To solve this, we need to calculate the net progress of the snail each day. 
+The snail climbs 3 feet up and slips back 2 feet, so the net progress is 3 - 2 = 1 foot per day.
+Since the well is 20 feet deep, the snail needs to make 20 feet of net progress. 
+20 feet / 1 foot per day = 20 days.
+The snail will reach the top of the well on the 20th day.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21T18:02:11.948754+00:00</t>
+          <t>2026-10-22T04:33:37.210823+00:00</t>
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.8972782359999201</v>
+        <v>1.032476554999903</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.9294981279999774</v>
+        <v>91</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>91</v>
-      </c>
-      <c r="J8" s="2" t="n">
-        <v>77</v>
-      </c>
-      <c r="K8" s="2" t="inlineStr"/>
+        <v>105</v>
+      </c>
+      <c r="J8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -837,29 +815,26 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>To solve this, we need to calculate the net progress the snail makes each day. 
-The snail climbs 3 feet up and slips back 2 feet, so it makes a net progress of 3 - 2 = 1 foot per day.
+          <t>To solve this, we need to calculate the net progress of the snail each day. 
+The snail climbs 3 feet and slips back 2 feet, so it makes a net progress of 3 - 2 = 1 foot per day.
 Since the well is 20 feet deep, the snail will need 20 days to climb 20 feet.</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21T18:02:12.878598+00:00</t>
+          <t>2026-10-22T04:33:38.243524+00:00</t>
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.7869334700001218</v>
+        <v>0.7844561639999483</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>0.8011711220001416</v>
+        <v>91</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>91</v>
-      </c>
-      <c r="J9" s="2" t="n">
-        <v>77</v>
-      </c>
-      <c r="K9" s="2" t="inlineStr"/>
+        <v>76</v>
+      </c>
+      <c r="J9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -880,34 +855,29 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>To solve this, we need to calculate the net progress the snail makes each day.
+          <t>To solve this, we need to calculate the net progress of the snail each day. 
 The snail climbs 3 feet up and slips back 2 feet, so it makes a net progress of 3 - 2 = 1 foot per day.
-Since the well is 20 feet deep, the snail needs to make 20 feet of progress. 
-20 feet / 1 foot per day = 20 days
-It will take the snail 20 days to reach the top of the well.</t>
+Since the well is 20 feet deep, the snail will need 20 days to climb 20 feet.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21T18:02:13.680012+00:00</t>
+          <t>2026-10-22T04:33:39.028209+00:00</t>
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>1.012311302999933</v>
+        <v>0.7863934920001157</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>1.032627935999926</v>
+        <v>91</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>91</v>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>105</v>
-      </c>
-      <c r="K10" s="2" t="inlineStr"/>
+        <v>77</v>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K10"/>
+  <autoFilter ref="A1:J10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -979,7 +949,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1007,10 +977,12 @@
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>{
-  "median_ttft": 0.877,
-  "median_latency": 0.917,
+  "median_input": 79,
+  "median_output": 93,
+  "median_latency": 0.799,
   "correct_frequency": 0.8333333333333334,
-  "misinformation_frequency": 0
+  "misinformation_frequency": 0,
+  "relevance_frequency": 1
 }</t>
         </is>
       </c>
@@ -1018,45 +990,65 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>median_ttft</t>
+          <t>median_input</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>0.877</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>median_latency</t>
+          <t>median_output</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0.917</v>
+        <v>93</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>correct_frequency</t>
+          <t>median_latency</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.799</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>correct_frequency</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
           <t>misinformation_frequency</t>
         </is>
       </c>
-      <c r="B6" s="2" t="n">
+      <c r="B7" s="2" t="n">
         <v>0</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>relevance_frequency</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B6"/>
+  <autoFilter ref="A1:B8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1094,7 +1086,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21T18:02:15.869667+00:00</t>
+          <t>2026-10-22T04:33:41.232448+00:00</t>
         </is>
       </c>
     </row>
